--- a/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Multe per violazioni al Codice della Strada.xlsx
+++ b/docs/0OMsoqOg9GiJ2xusVHM2/.gitbook/assets/IO - Template servizi - Multe per violazioni al Codice della Strada.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="77">
   <si>
     <r>
       <rPr>
@@ -185,7 +185,7 @@
     <t>Utilizza il testo indicato per il pulsante. Inserisci il link alla pagina web che rimanda al servizio.</t>
   </si>
   <si>
-    <t>n/a</t>
+    <t>Vai al servizio</t>
   </si>
   <si>
     <t>Link a termini e condizioni d'uso</t>
@@ -483,7 +483,7 @@
         <color indexed="8"/>
         <rFont val="Titillium Web Regular"/>
       </rPr>
-      <t>• </t>
+      <t xml:space="preserve">• </t>
     </r>
     <r>
       <rPr>
@@ -649,7 +649,7 @@
         <color indexed="8"/>
         <rFont val="Titillium Web Regular"/>
       </rPr>
-      <t xml:space="preserve">? Riceverai il verbale di contravvenzione in base a quanto previsto dal Codice della Strada e potranno essere addebitate le spese di notifica. 
+      <t xml:space="preserve">? Riceverai il verbale di contravvenzione in base a quanto previsto dal Codice della Strada e potranno essere addebitate le spese di notifica.
 </t>
     </r>
     <r>
@@ -667,7 +667,7 @@
         <color indexed="20"/>
         <rFont val="Titillium Web Regular"/>
       </rPr>
-      <t>[Se previsto dal tipo di multa]</t>
+      <t>[Se previsto]</t>
     </r>
     <r>
       <rPr>
@@ -723,24 +723,6 @@
       <t xml:space="preserve">
 </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Titillium Web Regular"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color indexed="8"/>
-        <rFont val="Titillium Web Regular"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
   </si>
   <si>
     <r>
@@ -765,7 +747,7 @@
         <color indexed="8"/>
         <rFont val="Titillium Web Regular"/>
       </rPr>
-      <t xml:space="preserve">. Lo riceverai nei prossimi giorni. 
+      <t xml:space="preserve">. Lo riceverai nei prossimi giorni.
 </t>
     </r>
     <r>
@@ -815,7 +797,14 @@
     </r>
   </si>
   <si>
-    <t>Vedi accertamento</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color indexed="8"/>
+        <rFont val="Titillium Web Regular"/>
+      </rPr>
+      <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
+    </r>
   </si>
   <si>
     <t>-</t>
@@ -855,7 +844,7 @@
         <color indexed="8"/>
         <rFont val="Titillium Web Regular"/>
       </rPr>
-      <t>Paga (inserito automaticamente dall'app se il messaggio prevede un avviso di pagamento pagoPA)</t>
+      <t>Vedi accertamento</t>
     </r>
   </si>
   <si>
@@ -866,7 +855,7 @@
         <color indexed="8"/>
         <rFont val="Verdana"/>
       </rPr>
-      <t>Allegato (Premium)</t>
+      <t>Allegato</t>
     </r>
     <r>
       <rPr>
@@ -964,9 +953,6 @@
       </rPr>
       <t>Note aggiuntive</t>
     </r>
-  </si>
-  <si>
-    <t>✨ Messaggio Premium — Se hai un contratto Premium, ti consigliamo di configurare questo messaggio con promemoria Premium: i destinatari verranno avvisati dell‘avvicinarsi della scadenza tramite notifica push.</t>
   </si>
 </sst>
 </file>
@@ -1277,7 +1263,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1468,6 +1454,9 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="4" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -32212,7 +32201,7 @@
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
     </row>
-    <row r="5" ht="543" customHeight="1">
+    <row r="5" ht="498" customHeight="1">
       <c r="A5" t="s" s="59">
         <v>61</v>
       </c>
@@ -32225,7 +32214,7 @@
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
     </row>
-    <row r="6" ht="39" customHeight="1">
+    <row r="6" ht="48" customHeight="1">
       <c r="A6" t="s" s="59">
         <v>64</v>
       </c>
@@ -32238,7 +32227,7 @@
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
     </row>
-    <row r="7" ht="48" customHeight="1">
+    <row r="7" ht="39" customHeight="1">
       <c r="A7" t="s" s="59">
         <v>67</v>
       </c>
@@ -32288,13 +32277,11 @@
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" ht="80" customHeight="1">
+    <row r="11" ht="18" customHeight="1">
       <c r="A11" t="s" s="63">
         <v>76</v>
       </c>
-      <c r="B11" t="s" s="60">
-        <v>77</v>
-      </c>
+      <c r="B11" s="64"/>
       <c r="C11" s="62"/>
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
